--- a/DateBase/orders/Nha Thu_2026-9-20.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-20.xlsx
@@ -761,6 +761,9 @@
       <c r="G2" t="str">
         <v>030162109201775105101020101515101010105884105101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
